--- a/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T15:07:43+00:00</t>
+    <t>2023-10-23T11:38:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T11:38:46+00:00</t>
+    <t>2023-11-06T10:27:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T10:27:25+00:00</t>
+    <t>2023-11-06T10:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T10:34:42+00:00</t>
+    <t>2023-11-06T13:10:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:10:33+00:00</t>
+    <t>2023-11-06T13:11:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:11:32+00:00</t>
+    <t>2023-11-06T13:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/nr-add-def-ins-collection/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T13:13:14+00:00</t>
+    <t>2023-11-06T13:13:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
